--- a/data/trans_orig/IP09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65593</t>
+          <t>65240</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>23985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34719</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>110749</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>132825</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>30735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69126</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91363</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
